--- a/Pattern Match/Against training/output/rientra_matching.xlsx
+++ b/Pattern Match/Against training/output/rientra_matching.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,8 +66,14 @@
       <color rgb="00A32D2D"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="005C2D91"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -104,11 +110,6 @@
         <fgColor rgb="00D0FBE0"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FBE4D0"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -136,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -171,12 +172,6 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -189,10 +184,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -204,7 +202,7 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -572,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U10"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -592,10 +590,7 @@
     <col width="32" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="55" customWidth="1" min="17" max="17"/>
-    <col width="32" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="55" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -686,21 +681,6 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>S5 · GloVe-6B-300d (Stanford NLP) Match</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>S5 · Score</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>S5 · O*NET URI</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
           <t>Verdetto</t>
         </is>
       </c>
@@ -763,7 +743,7 @@
         </is>
       </c>
       <c r="M2" s="9" t="n">
-        <v>0.9801</v>
+        <v>0.983</v>
       </c>
       <c r="N2" s="8" t="inlineStr">
         <is>
@@ -785,40 +765,27 @@
       </c>
       <c r="R2" s="12" t="inlineStr">
         <is>
-          <t>Bookkeeping, Accounting, and Auditing Clerks</t>
-        </is>
-      </c>
-      <c r="S2" s="13" t="n">
-        <v>0.9454</v>
-      </c>
-      <c r="T2" s="12" t="inlineStr">
-        <is>
-          <t>http://www.stiima.cnr.it/JobList#Bookkeping_accounting_and_auditing_clerks</t>
-        </is>
-      </c>
-      <c r="U2" s="14" t="inlineStr">
-        <is>
           <t>Accordo parziale</t>
         </is>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>ext02</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>Content manager web</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>Plan, create, manage, and update digital content for websites and online platforms. Coordinate the development of text, images, and multimedia materials to ensure consistency with organizational goals. Monitor content performance, maintain site structure, and collaborate with designers, editors, and marketing staff.</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>https://www.stiima.cnr.it/rientra#ExtJob_ext02</t>
         </is>
@@ -841,15 +808,15 @@
           <t>http://www.stiima.cnr.it/JobList#Billing_cost_and_rate_clerks</t>
         </is>
       </c>
-      <c r="I3" s="17" t="inlineStr">
+      <c r="I3" s="15" t="inlineStr">
         <is>
           <t>sotto soglia (raw 0.345)</t>
         </is>
       </c>
-      <c r="J3" s="15" t="n">
+      <c r="J3" s="13" t="n">
         <v>0.3455</v>
       </c>
-      <c r="K3" s="17" t="inlineStr">
+      <c r="K3" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -860,42 +827,29 @@
         </is>
       </c>
       <c r="M3" s="9" t="n">
-        <v>0.8862</v>
+        <v>0.8923</v>
       </c>
       <c r="N3" s="8" t="inlineStr">
         <is>
           <t>http://www.stiima.cnr.it/JobList#Receptionist_and_information_clerks</t>
         </is>
       </c>
-      <c r="O3" s="17" t="inlineStr">
+      <c r="O3" s="15" t="inlineStr">
         <is>
           <t>sotto soglia (raw 0.268)</t>
         </is>
       </c>
-      <c r="P3" s="15" t="n">
+      <c r="P3" s="13" t="n">
         <v>0.2676</v>
       </c>
-      <c r="Q3" s="17" t="inlineStr">
+      <c r="Q3" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R3" s="12" t="inlineStr">
-        <is>
-          <t>Insurance Policy Processing Clerks</t>
-        </is>
-      </c>
-      <c r="S3" s="13" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="T3" s="12" t="inlineStr">
-        <is>
-          <t>http://www.stiima.cnr.it/JobList#Insurance_policy_processing_clerks</t>
-        </is>
-      </c>
-      <c r="U3" s="18" t="inlineStr">
-        <is>
-          <t>Divergono</t>
+      <c r="R3" s="16" t="inlineStr">
+        <is>
+          <t>Accordo parziale</t>
         </is>
       </c>
     </row>
@@ -938,7 +892,7 @@
           <t>http://www.stiima.cnr.it/JobList#Insurance_policy_processing_clerks</t>
         </is>
       </c>
-      <c r="I4" s="19" t="inlineStr">
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t>sotto soglia (raw 0.490)</t>
         </is>
@@ -946,25 +900,25 @@
       <c r="J4" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="K4" s="19" t="inlineStr">
+      <c r="K4" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L4" s="19" t="inlineStr">
-        <is>
-          <t>sotto soglia (raw 0.432)</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>0.4317</v>
-      </c>
-      <c r="N4" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O4" s="19" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>Word Processors and Typists</t>
+        </is>
+      </c>
+      <c r="M4" s="18" t="n">
+        <v>0.5351</v>
+      </c>
+      <c r="N4" s="8" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Word_Processors_and_Typists</t>
+        </is>
+      </c>
+      <c r="O4" s="17" t="inlineStr">
         <is>
           <t>sotto soglia (raw 0.381)</t>
         </is>
@@ -972,47 +926,34 @@
       <c r="P4" s="2" t="n">
         <v>0.3807</v>
       </c>
-      <c r="Q4" s="19" t="inlineStr">
+      <c r="Q4" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="R4" s="12" t="inlineStr">
         <is>
-          <t>Insurance Policy Processing Clerks</t>
-        </is>
-      </c>
-      <c r="S4" s="13" t="n">
-        <v>0.8354</v>
-      </c>
-      <c r="T4" s="12" t="inlineStr">
-        <is>
-          <t>http://www.stiima.cnr.it/JobList#Insurance_policy_processing_clerks</t>
-        </is>
-      </c>
-      <c r="U4" s="14" t="inlineStr">
-        <is>
           <t>Accordo parziale</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>ext04</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Data entry</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>Enter numerical and text data into computer systems or databases using keyboards, data recorders, or scanners. Verify accuracy of data, correct errors, and maintain confidentiality of information. May compile, sort, and organize source documents.</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>https://www.stiima.cnr.it/rientra#ExtJob_ext04</t>
         </is>
@@ -1040,7 +981,7 @@
           <t>Word Processors and Typists</t>
         </is>
       </c>
-      <c r="J5" s="20" t="n">
+      <c r="J5" s="19" t="n">
         <v>0.5488</v>
       </c>
       <c r="K5" s="6" t="inlineStr">
@@ -1048,48 +989,35 @@
           <t>http://www.stiima.cnr.it/JobList#Word_Processors_and_Typists</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>Word Processors and Typists</t>
+        </is>
+      </c>
+      <c r="M5" s="9" t="n">
+        <v>0.7324000000000001</v>
+      </c>
+      <c r="N5" s="8" t="inlineStr">
+        <is>
+          <t>http://www.stiima.cnr.it/JobList#Word_Processors_and_Typists</t>
+        </is>
+      </c>
+      <c r="O5" s="15" t="inlineStr">
         <is>
           <t>sotto soglia (raw 0.489)</t>
         </is>
       </c>
-      <c r="M5" s="15" t="n">
-        <v>0.4895</v>
-      </c>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="P5" s="13" t="n">
+        <v>0.4887</v>
+      </c>
+      <c r="Q5" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O5" s="17" t="inlineStr">
-        <is>
-          <t>sotto soglia (raw 0.489)</t>
-        </is>
-      </c>
-      <c r="P5" s="15" t="n">
-        <v>0.4887</v>
-      </c>
-      <c r="Q5" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R5" s="12" t="inlineStr">
-        <is>
-          <t>Bookkeeping, Accounting, and Auditing Clerks</t>
-        </is>
-      </c>
-      <c r="S5" s="13" t="n">
-        <v>0.8266</v>
-      </c>
-      <c r="T5" s="12" t="inlineStr">
-        <is>
-          <t>http://www.stiima.cnr.it/JobList#Bookkeping_accounting_and_auditing_clerks</t>
-        </is>
-      </c>
-      <c r="U5" s="18" t="inlineStr">
-        <is>
-          <t>Divergono</t>
+      <c r="R5" s="16" t="inlineStr">
+        <is>
+          <t>Accordo parziale</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1065,7 @@
           <t>Word Processors and Typists</t>
         </is>
       </c>
-      <c r="J6" s="20" t="n">
+      <c r="J6" s="19" t="n">
         <v>0.5396</v>
       </c>
       <c r="K6" s="6" t="inlineStr">
@@ -1151,7 +1079,7 @@
         </is>
       </c>
       <c r="M6" s="9" t="n">
-        <v>0.735</v>
+        <v>0.8964</v>
       </c>
       <c r="N6" s="8" t="inlineStr">
         <is>
@@ -1163,7 +1091,7 @@
           <t>Bookkeeping, Accounting, and Auditing Clerks</t>
         </is>
       </c>
-      <c r="P6" s="21" t="n">
+      <c r="P6" s="20" t="n">
         <v>0.5558999999999999</v>
       </c>
       <c r="Q6" s="10" t="inlineStr">
@@ -1171,42 +1099,29 @@
           <t>http://www.stiima.cnr.it/JobList#Bookkeping_accounting_and_auditing_clerks</t>
         </is>
       </c>
-      <c r="R6" s="12" t="inlineStr">
-        <is>
-          <t>Insurance Policy Processing Clerks</t>
-        </is>
-      </c>
-      <c r="S6" s="13" t="n">
-        <v>0.8868</v>
-      </c>
-      <c r="T6" s="12" t="inlineStr">
-        <is>
-          <t>http://www.stiima.cnr.it/JobList#Insurance_policy_processing_clerks</t>
-        </is>
-      </c>
-      <c r="U6" s="22" t="inlineStr">
+      <c r="R6" s="21" t="inlineStr">
         <is>
           <t>Divergono</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>ext06</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Data scientist</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>Develop and apply statistical, mathematical, and computational techniques to analyze large and complex data sets. Build models to extract insights, make predictions, and support strategic decisions. Communicate analytical results through reports, visualizations, and presentations.</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>https://www.stiima.cnr.it/rientra#ExtJob_ext06</t>
         </is>
@@ -1229,61 +1144,48 @@
           <t>http://www.stiima.cnr.it/JobList#Insurance_policy_processing_clerks</t>
         </is>
       </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="I7" s="15" t="inlineStr">
         <is>
           <t>sotto soglia (raw 0.352)</t>
         </is>
       </c>
-      <c r="J7" s="15" t="n">
+      <c r="J7" s="13" t="n">
         <v>0.3523</v>
       </c>
-      <c r="K7" s="17" t="inlineStr">
+      <c r="K7" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
-        <is>
-          <t>sotto soglia (raw 0.305)</t>
-        </is>
-      </c>
-      <c r="M7" s="15" t="n">
-        <v>0.3051</v>
-      </c>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="L7" s="15" t="inlineStr">
+        <is>
+          <t>sotto soglia (raw 0.400)</t>
+        </is>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>0.4003</v>
+      </c>
+      <c r="N7" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O7" s="17" t="inlineStr">
+      <c r="O7" s="15" t="inlineStr">
         <is>
           <t>sotto soglia (raw 0.357)</t>
         </is>
       </c>
-      <c r="P7" s="15" t="n">
+      <c r="P7" s="13" t="n">
         <v>0.3574</v>
       </c>
-      <c r="Q7" s="17" t="inlineStr">
+      <c r="Q7" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R7" s="12" t="inlineStr">
-        <is>
-          <t>Insurance Policy Processing Clerks</t>
-        </is>
-      </c>
-      <c r="S7" s="13" t="n">
-        <v>0.7755</v>
-      </c>
-      <c r="T7" s="12" t="inlineStr">
-        <is>
-          <t>http://www.stiima.cnr.it/JobList#Insurance_policy_processing_clerks</t>
-        </is>
-      </c>
-      <c r="U7" s="23" t="inlineStr">
-        <is>
-          <t>Accordo parziale</t>
+      <c r="R7" s="22" t="inlineStr">
+        <is>
+          <t>Solo S1</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1228,7 @@
           <t>http://www.stiima.cnr.it/JobList#File_clerks</t>
         </is>
       </c>
-      <c r="I8" s="19" t="inlineStr">
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>sotto soglia (raw 0.410)</t>
         </is>
@@ -1334,7 +1236,7 @@
       <c r="J8" s="2" t="n">
         <v>0.4101</v>
       </c>
-      <c r="K8" s="19" t="inlineStr">
+      <c r="K8" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1345,14 +1247,14 @@
         </is>
       </c>
       <c r="M8" s="9" t="n">
-        <v>0.8905</v>
+        <v>0.8776</v>
       </c>
       <c r="N8" s="8" t="inlineStr">
         <is>
           <t>http://www.stiima.cnr.it/JobList#Receptionist_and_information_clerks</t>
         </is>
       </c>
-      <c r="O8" s="19" t="inlineStr">
+      <c r="O8" s="17" t="inlineStr">
         <is>
           <t>sotto soglia (raw 0.363)</t>
         </is>
@@ -1360,47 +1262,34 @@
       <c r="P8" s="2" t="n">
         <v>0.3634</v>
       </c>
-      <c r="Q8" s="19" t="inlineStr">
+      <c r="Q8" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="R8" s="12" t="inlineStr">
         <is>
-          <t>Insurance Policy Processing Clerks</t>
-        </is>
-      </c>
-      <c r="S8" s="13" t="n">
-        <v>0.8142</v>
-      </c>
-      <c r="T8" s="12" t="inlineStr">
-        <is>
-          <t>http://www.stiima.cnr.it/JobList#Insurance_policy_processing_clerks</t>
-        </is>
-      </c>
-      <c r="U8" s="22" t="inlineStr">
-        <is>
-          <t>Divergono</t>
+          <t>Accordo parziale</t>
         </is>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>ext08</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Switchboard operator</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>Operate telephone switchboard systems to route incoming, outgoing, and interoffice calls. Provide information to callers, take messages, and announce visitors. May handle answering services and perform related administrative tasks.</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>https://www.stiima.cnr.it/rientra#ExtJob_ext08</t>
         </is>
@@ -1428,7 +1317,7 @@
           <t>Receptionists and Information Clerks</t>
         </is>
       </c>
-      <c r="J9" s="20" t="n">
+      <c r="J9" s="19" t="n">
         <v>0.6401</v>
       </c>
       <c r="K9" s="6" t="inlineStr">
@@ -1442,40 +1331,27 @@
         </is>
       </c>
       <c r="M9" s="9" t="n">
-        <v>0.8032</v>
+        <v>0.8323</v>
       </c>
       <c r="N9" s="8" t="inlineStr">
         <is>
           <t>http://www.stiima.cnr.it/JobList#Receptionist_and_information_clerks</t>
         </is>
       </c>
-      <c r="O9" s="17" t="inlineStr">
+      <c r="O9" s="15" t="inlineStr">
         <is>
           <t>sotto soglia (raw 0.319)</t>
         </is>
       </c>
-      <c r="P9" s="15" t="n">
+      <c r="P9" s="13" t="n">
         <v>0.319</v>
       </c>
-      <c r="Q9" s="17" t="inlineStr">
+      <c r="Q9" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R9" s="12" t="inlineStr">
-        <is>
-          <t>Receptionists and Information Clerks</t>
-        </is>
-      </c>
-      <c r="S9" s="13" t="n">
-        <v>0.8276</v>
-      </c>
-      <c r="T9" s="12" t="inlineStr">
-        <is>
-          <t>http://www.stiima.cnr.it/JobList#Receptionist_and_information_clerks</t>
-        </is>
-      </c>
-      <c r="U9" s="23" t="inlineStr">
+      <c r="R9" s="16" t="inlineStr">
         <is>
           <t>Accordo parziale</t>
         </is>
@@ -1502,27 +1378,27 @@
           <t>https://www.stiima.cnr.it/rientra#ExtJob_ext09</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H10" s="19" t="inlineStr">
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I10" s="19" t="inlineStr">
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>sotto soglia (raw 0.499)</t>
         </is>
@@ -1530,7 +1406,7 @@
       <c r="J10" s="2" t="n">
         <v>0.499</v>
       </c>
-      <c r="K10" s="19" t="inlineStr">
+      <c r="K10" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1540,8 +1416,8 @@
           <t>Bookkeeping, Accounting, and Auditing Clerks</t>
         </is>
       </c>
-      <c r="M10" s="9" t="n">
-        <v>0.7256</v>
+      <c r="M10" s="18" t="n">
+        <v>0.699</v>
       </c>
       <c r="N10" s="8" t="inlineStr">
         <is>
@@ -1553,7 +1429,7 @@
           <t>Billing, Cost, and Rate Clerks</t>
         </is>
       </c>
-      <c r="P10" s="21" t="n">
+      <c r="P10" s="20" t="n">
         <v>0.5111</v>
       </c>
       <c r="Q10" s="10" t="inlineStr">
@@ -1561,20 +1437,7 @@
           <t>http://www.stiima.cnr.it/JobList#Billing_cost_and_rate_clerks</t>
         </is>
       </c>
-      <c r="R10" s="12" t="inlineStr">
-        <is>
-          <t>Billing, Cost, and Rate Clerks</t>
-        </is>
-      </c>
-      <c r="S10" s="13" t="n">
-        <v>0.8843</v>
-      </c>
-      <c r="T10" s="12" t="inlineStr">
-        <is>
-          <t>http://www.stiima.cnr.it/JobList#Billing_cost_and_rate_clerks</t>
-        </is>
-      </c>
-      <c r="U10" s="22" t="inlineStr">
+      <c r="R10" s="21" t="inlineStr">
         <is>
           <t>Divergono</t>
         </is>
@@ -1629,25 +1492,25 @@
       </c>
     </row>
     <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="15" t="n">
+      <c r="A2" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>Billing_cost_and_rate_clerks</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>Billing, Cost, and Rate Clerks</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>Accounting Assistant, Accounting Clerk, Accounts Payable Clerk, Accounts Receivable Clerk, Administrative Assistant, Biller, Billing Clerk, Billing Coordinator, Billing Specialist, Office Manager</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>Compile data, compute fees and charges, and prepare invoices for billing purposes. Duties include computing costs and calculating rates for goods, services, and shipment of goods; posting data; and keeping other relevant records. May involve use of computer or typewriter, calculator, and adding and bookkeeping machines.</t>
         </is>
@@ -1679,25 +1542,25 @@
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="15" t="n">
+      <c r="A4" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Cabinet_makers_and_bench_carpenters</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>Cabinetmakers and Bench Carpenters</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>Cabinet Assembler, Cabinet Builder, Cabinet Installer, Cabinetmaker, Cutter, Double End Tenon Operator, Frame Builder, Framer, Machine Operator, Woodworker</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>Cut, shape, and assemble wooden articles or set up and operate a variety of woodworking machines, such as power saws, jointers, and mortisers to surface, cut, or shape lumber or to fabricate parts for wood products.</t>
         </is>
@@ -1729,25 +1592,25 @@
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="15" t="n">
+      <c r="A6" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>File_clerks</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>File Clerks</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Claims Clerk, Clerk, Documentation Specialist, File Clerk, Human Resources Assistant (HR Assistant), Manufacturing Clerk, Medical Records Clerk, Office Assistant, Police Records Clerk, Records Clerk</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>File correspondence, cards, invoices, receipts, and other records in alphabetical or numerical order or according to the filing system used. Locate and remove material from file when requested.</t>
         </is>
@@ -1779,25 +1642,25 @@
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>Insurance_claims_clerks</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>Insurance Claims Clerks</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>Call Center Representative, Claim Processing Specialist, Claim Service Representative, Claim Technician, Claims Clerk, Claims Customer Service Representative (Claims CSR), Claims Processor, Claims Representative, Claims Service Representative, Claims Technician</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>Obtain information from insured or designated persons for purpose of settling claim with insurance carrier.</t>
         </is>
@@ -1829,25 +1692,25 @@
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="15" t="n">
+      <c r="A10" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Landscaping_and_Groundskeeping_Workers</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>Landscaping and Groundskeeping Workers</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>Gardener, Greenskeeper, Grounds Maintenance Worker, Grounds Person, Grounds Worker, Grounds/Maintenance Specialist, Groundskeeper, Landscape Specialist, Landscape Technician, Outside Maintenance Worker</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>Landscape or maintain grounds of property using hand or power tools or equipment. Workers typically perform a variety of tasks, which may include any combination of the following: sod laying, mowing, trimming, planting, watering, fertilizing, digging, raking, sprinkler installation, and installation of mortarless segmental concrete masonry wall units.</t>
         </is>
@@ -1879,25 +1742,25 @@
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="15" t="n">
+      <c r="A12" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>Receptionist_and_information_clerks</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>Receptionists and Information Clerks</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>Clerk Specialist, Community Liaison, Front Desk Receptionist, Greeter, Member Service Representative, Office Assistant, Receptionist, Scheduler, Senior Receptionist, Unit Assistant</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>Answer inquiries and provide information to the general public, customers, visitors, and other interested parties regarding activities conducted at establishment and location of departments, offices, and employees within the organization.</t>
         </is>
@@ -1929,25 +1792,25 @@
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="15" t="n">
+      <c r="A14" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>Word_Processors_and_Typists</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>Word Processors and Typists</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>Clerk Specialist, Clerk Typist, Keyboard Specialist, Management Services Technician, Office Technician, Principal Clerk Typist, Project Assistant, Stenographer, Typist, Word Processor</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>Use word processor, computer or typewriter to type letters, reports, forms, or other material from rough draft, corrected copy, or voice recording. May perform other clerical duties as assigned.</t>
         </is>
@@ -1964,7 +1827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB10"/>
+  <dimension ref="A1:AO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2008,19 +1871,6 @@
     <col width="14" customWidth="1" min="39" max="39"/>
     <col width="14" customWidth="1" min="40" max="40"/>
     <col width="14" customWidth="1" min="41" max="41"/>
-    <col width="14" customWidth="1" min="42" max="42"/>
-    <col width="14" customWidth="1" min="43" max="43"/>
-    <col width="14" customWidth="1" min="44" max="44"/>
-    <col width="14" customWidth="1" min="45" max="45"/>
-    <col width="14" customWidth="1" min="46" max="46"/>
-    <col width="14" customWidth="1" min="47" max="47"/>
-    <col width="14" customWidth="1" min="48" max="48"/>
-    <col width="14" customWidth="1" min="49" max="49"/>
-    <col width="14" customWidth="1" min="50" max="50"/>
-    <col width="14" customWidth="1" min="51" max="51"/>
-    <col width="14" customWidth="1" min="52" max="52"/>
-    <col width="14" customWidth="1" min="53" max="53"/>
-    <col width="14" customWidth="1" min="54" max="54"/>
   </cols>
   <sheetData>
     <row r="1" ht="45" customHeight="1">
@@ -2265,84 +2115,6 @@
       <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>all-MiniLM-L6-v2
-Word Processors and Ty</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>GloVe-6B-300d (Stanford NLP)
-Billing, Cost, and Rat</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>GloVe-6B-300d (Stanford NLP)
-Bookkeeping, Accountin</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>GloVe-6B-300d (Stanford NLP)
-Cabinetmakers and Benc</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>GloVe-6B-300d (Stanford NLP)
-Construction laborers</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>GloVe-6B-300d (Stanford NLP)
-File Clerks</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>GloVe-6B-300d (Stanford NLP)
-Gem and Diamond Worker</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>GloVe-6B-300d (Stanford NLP)
-Insurance Claims Clerk</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>GloVe-6B-300d (Stanford NLP)
-Insurance Policy Proce</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>GloVe-6B-300d (Stanford NLP)
-Landscaping and Ground</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>GloVe-6B-300d (Stanford NLP)
-Postal Service Clerks</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>GloVe-6B-300d (Stanford NLP)
-Receptionists and Info</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>GloVe-6B-300d (Stanford NLP)
-Travel guides</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>GloVe-6B-300d (Stanford NLP)
 Word Processors and Ty</t>
         </is>
       </c>
@@ -2375,7 +2147,7 @@
       <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="9" t="n">
-        <v>0.9801</v>
+        <v>0.983</v>
       </c>
       <c r="R2" s="2" t="n"/>
       <c r="S2" s="2" t="n"/>
@@ -2403,89 +2175,59 @@
       <c r="AM2" s="2" t="n"/>
       <c r="AN2" s="2" t="n"/>
       <c r="AO2" s="2" t="n"/>
-      <c r="AP2" s="2" t="n"/>
-      <c r="AQ2" s="13" t="n">
-        <v>0.9454</v>
-      </c>
-      <c r="AR2" s="2" t="n"/>
-      <c r="AS2" s="2" t="n"/>
-      <c r="AT2" s="2" t="n"/>
-      <c r="AU2" s="2" t="n"/>
-      <c r="AV2" s="2" t="n"/>
-      <c r="AW2" s="2" t="n"/>
-      <c r="AX2" s="2" t="n"/>
-      <c r="AY2" s="2" t="n"/>
-      <c r="AZ2" s="2" t="n"/>
-      <c r="BA2" s="2" t="n"/>
-      <c r="BB2" s="2" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>ext02</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Content manager web</t>
         </is>
       </c>
-      <c r="C3" s="15" t="n"/>
-      <c r="D3" s="15" t="n"/>
-      <c r="E3" s="15" t="n"/>
-      <c r="F3" s="15" t="n"/>
-      <c r="G3" s="15" t="n"/>
-      <c r="H3" s="15" t="n"/>
-      <c r="I3" s="15" t="n"/>
-      <c r="J3" s="15" t="n"/>
-      <c r="K3" s="15" t="n"/>
-      <c r="L3" s="15" t="n"/>
-      <c r="M3" s="15" t="n"/>
-      <c r="N3" s="15" t="n"/>
-      <c r="O3" s="15" t="n"/>
-      <c r="P3" s="15" t="n"/>
-      <c r="Q3" s="15" t="n"/>
-      <c r="R3" s="15" t="n"/>
-      <c r="S3" s="15" t="n"/>
-      <c r="T3" s="15" t="n"/>
-      <c r="U3" s="15" t="n"/>
-      <c r="V3" s="15" t="n"/>
-      <c r="W3" s="15" t="n"/>
-      <c r="X3" s="15" t="n"/>
-      <c r="Y3" s="15" t="n"/>
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="13" t="n"/>
+      <c r="G3" s="13" t="n"/>
+      <c r="H3" s="13" t="n"/>
+      <c r="I3" s="13" t="n"/>
+      <c r="J3" s="13" t="n"/>
+      <c r="K3" s="13" t="n"/>
+      <c r="L3" s="13" t="n"/>
+      <c r="M3" s="13" t="n"/>
+      <c r="N3" s="13" t="n"/>
+      <c r="O3" s="13" t="n"/>
+      <c r="P3" s="13" t="n"/>
+      <c r="Q3" s="13" t="n"/>
+      <c r="R3" s="13" t="n"/>
+      <c r="S3" s="13" t="n"/>
+      <c r="T3" s="13" t="n"/>
+      <c r="U3" s="13" t="n"/>
+      <c r="V3" s="13" t="n"/>
+      <c r="W3" s="13" t="n"/>
+      <c r="X3" s="13" t="n"/>
+      <c r="Y3" s="13" t="n"/>
       <c r="Z3" s="9" t="n">
-        <v>0.8862</v>
-      </c>
-      <c r="AA3" s="15" t="n"/>
-      <c r="AB3" s="15" t="n"/>
-      <c r="AC3" s="15" t="n"/>
-      <c r="AD3" s="15" t="n"/>
-      <c r="AE3" s="15" t="n"/>
-      <c r="AF3" s="15" t="n"/>
-      <c r="AG3" s="15" t="n"/>
-      <c r="AH3" s="15" t="n"/>
-      <c r="AI3" s="15" t="n"/>
-      <c r="AJ3" s="15" t="n"/>
-      <c r="AK3" s="15" t="n"/>
-      <c r="AL3" s="15" t="n"/>
-      <c r="AM3" s="15" t="n"/>
-      <c r="AN3" s="15" t="n"/>
-      <c r="AO3" s="15" t="n"/>
-      <c r="AP3" s="15" t="n"/>
-      <c r="AQ3" s="15" t="n"/>
-      <c r="AR3" s="15" t="n"/>
-      <c r="AS3" s="15" t="n"/>
-      <c r="AT3" s="15" t="n"/>
-      <c r="AU3" s="15" t="n"/>
-      <c r="AV3" s="15" t="n"/>
-      <c r="AW3" s="13" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="AX3" s="15" t="n"/>
-      <c r="AY3" s="15" t="n"/>
-      <c r="AZ3" s="15" t="n"/>
-      <c r="BA3" s="15" t="n"/>
-      <c r="BB3" s="15" t="n"/>
+        <v>0.8923</v>
+      </c>
+      <c r="AA3" s="13" t="n"/>
+      <c r="AB3" s="13" t="n"/>
+      <c r="AC3" s="13" t="n"/>
+      <c r="AD3" s="13" t="n"/>
+      <c r="AE3" s="13" t="n"/>
+      <c r="AF3" s="13" t="n"/>
+      <c r="AG3" s="13" t="n"/>
+      <c r="AH3" s="13" t="n"/>
+      <c r="AI3" s="13" t="n"/>
+      <c r="AJ3" s="13" t="n"/>
+      <c r="AK3" s="13" t="n"/>
+      <c r="AL3" s="13" t="n"/>
+      <c r="AM3" s="13" t="n"/>
+      <c r="AN3" s="13" t="n"/>
+      <c r="AO3" s="13" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -2523,7 +2265,9 @@
       <c r="Y4" s="2" t="n"/>
       <c r="Z4" s="2" t="n"/>
       <c r="AA4" s="2" t="n"/>
-      <c r="AB4" s="2" t="n"/>
+      <c r="AB4" s="18" t="n">
+        <v>0.5351</v>
+      </c>
       <c r="AC4" s="2" t="n"/>
       <c r="AD4" s="2" t="n"/>
       <c r="AE4" s="2" t="n"/>
@@ -2537,89 +2281,61 @@
       <c r="AM4" s="2" t="n"/>
       <c r="AN4" s="2" t="n"/>
       <c r="AO4" s="2" t="n"/>
-      <c r="AP4" s="2" t="n"/>
-      <c r="AQ4" s="2" t="n"/>
-      <c r="AR4" s="2" t="n"/>
-      <c r="AS4" s="2" t="n"/>
-      <c r="AT4" s="2" t="n"/>
-      <c r="AU4" s="2" t="n"/>
-      <c r="AV4" s="2" t="n"/>
-      <c r="AW4" s="13" t="n">
-        <v>0.8354</v>
-      </c>
-      <c r="AX4" s="2" t="n"/>
-      <c r="AY4" s="2" t="n"/>
-      <c r="AZ4" s="2" t="n"/>
-      <c r="BA4" s="2" t="n"/>
-      <c r="BB4" s="2" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>ext04</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Data entry</t>
         </is>
       </c>
-      <c r="C5" s="15" t="n"/>
-      <c r="D5" s="15" t="n"/>
-      <c r="E5" s="15" t="n"/>
-      <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
-      <c r="H5" s="15" t="n"/>
-      <c r="I5" s="15" t="n"/>
-      <c r="J5" s="15" t="n"/>
-      <c r="K5" s="15" t="n"/>
-      <c r="L5" s="15" t="n"/>
-      <c r="M5" s="15" t="n"/>
-      <c r="N5" s="15" t="n"/>
-      <c r="O5" s="20" t="n">
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="n"/>
+      <c r="H5" s="13" t="n"/>
+      <c r="I5" s="13" t="n"/>
+      <c r="J5" s="13" t="n"/>
+      <c r="K5" s="13" t="n"/>
+      <c r="L5" s="13" t="n"/>
+      <c r="M5" s="13" t="n"/>
+      <c r="N5" s="13" t="n"/>
+      <c r="O5" s="19" t="n">
         <v>0.5488</v>
       </c>
-      <c r="P5" s="15" t="n"/>
-      <c r="Q5" s="15" t="n"/>
-      <c r="R5" s="15" t="n"/>
-      <c r="S5" s="15" t="n"/>
-      <c r="T5" s="15" t="n"/>
-      <c r="U5" s="15" t="n"/>
-      <c r="V5" s="15" t="n"/>
-      <c r="W5" s="15" t="n"/>
-      <c r="X5" s="15" t="n"/>
-      <c r="Y5" s="15" t="n"/>
-      <c r="Z5" s="15" t="n"/>
-      <c r="AA5" s="15" t="n"/>
-      <c r="AB5" s="15" t="n"/>
-      <c r="AC5" s="15" t="n"/>
-      <c r="AD5" s="15" t="n"/>
-      <c r="AE5" s="15" t="n"/>
-      <c r="AF5" s="15" t="n"/>
-      <c r="AG5" s="15" t="n"/>
-      <c r="AH5" s="15" t="n"/>
-      <c r="AI5" s="15" t="n"/>
-      <c r="AJ5" s="15" t="n"/>
-      <c r="AK5" s="15" t="n"/>
-      <c r="AL5" s="15" t="n"/>
-      <c r="AM5" s="15" t="n"/>
-      <c r="AN5" s="15" t="n"/>
-      <c r="AO5" s="15" t="n"/>
-      <c r="AP5" s="15" t="n"/>
-      <c r="AQ5" s="13" t="n">
-        <v>0.8266</v>
-      </c>
-      <c r="AR5" s="15" t="n"/>
-      <c r="AS5" s="15" t="n"/>
-      <c r="AT5" s="15" t="n"/>
-      <c r="AU5" s="15" t="n"/>
-      <c r="AV5" s="15" t="n"/>
-      <c r="AW5" s="15" t="n"/>
-      <c r="AX5" s="15" t="n"/>
-      <c r="AY5" s="15" t="n"/>
-      <c r="AZ5" s="15" t="n"/>
-      <c r="BA5" s="15" t="n"/>
-      <c r="BB5" s="15" t="n"/>
+      <c r="P5" s="13" t="n"/>
+      <c r="Q5" s="13" t="n"/>
+      <c r="R5" s="13" t="n"/>
+      <c r="S5" s="13" t="n"/>
+      <c r="T5" s="13" t="n"/>
+      <c r="U5" s="13" t="n"/>
+      <c r="V5" s="13" t="n"/>
+      <c r="W5" s="13" t="n"/>
+      <c r="X5" s="13" t="n"/>
+      <c r="Y5" s="13" t="n"/>
+      <c r="Z5" s="13" t="n"/>
+      <c r="AA5" s="13" t="n"/>
+      <c r="AB5" s="9" t="n">
+        <v>0.7324000000000001</v>
+      </c>
+      <c r="AC5" s="13" t="n"/>
+      <c r="AD5" s="13" t="n"/>
+      <c r="AE5" s="13" t="n"/>
+      <c r="AF5" s="13" t="n"/>
+      <c r="AG5" s="13" t="n"/>
+      <c r="AH5" s="13" t="n"/>
+      <c r="AI5" s="13" t="n"/>
+      <c r="AJ5" s="13" t="n"/>
+      <c r="AK5" s="13" t="n"/>
+      <c r="AL5" s="13" t="n"/>
+      <c r="AM5" s="13" t="n"/>
+      <c r="AN5" s="13" t="n"/>
+      <c r="AO5" s="13" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -2644,7 +2360,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
-      <c r="O6" s="20" t="n">
+      <c r="O6" s="19" t="n">
         <v>0.5396</v>
       </c>
       <c r="P6" s="2" t="n"/>
@@ -2660,10 +2376,10 @@
       <c r="Z6" s="2" t="n"/>
       <c r="AA6" s="2" t="n"/>
       <c r="AB6" s="9" t="n">
-        <v>0.735</v>
+        <v>0.8964</v>
       </c>
       <c r="AC6" s="2" t="n"/>
-      <c r="AD6" s="21" t="n">
+      <c r="AD6" s="20" t="n">
         <v>0.5558999999999999</v>
       </c>
       <c r="AE6" s="2" t="n"/>
@@ -2677,87 +2393,57 @@
       <c r="AM6" s="2" t="n"/>
       <c r="AN6" s="2" t="n"/>
       <c r="AO6" s="2" t="n"/>
-      <c r="AP6" s="2" t="n"/>
-      <c r="AQ6" s="2" t="n"/>
-      <c r="AR6" s="2" t="n"/>
-      <c r="AS6" s="2" t="n"/>
-      <c r="AT6" s="2" t="n"/>
-      <c r="AU6" s="2" t="n"/>
-      <c r="AV6" s="2" t="n"/>
-      <c r="AW6" s="13" t="n">
-        <v>0.8868</v>
-      </c>
-      <c r="AX6" s="2" t="n"/>
-      <c r="AY6" s="2" t="n"/>
-      <c r="AZ6" s="2" t="n"/>
-      <c r="BA6" s="2" t="n"/>
-      <c r="BB6" s="2" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>ext06</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Data scientist</t>
         </is>
       </c>
-      <c r="C7" s="15" t="n"/>
-      <c r="D7" s="15" t="n"/>
-      <c r="E7" s="15" t="n"/>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
-      <c r="H7" s="15" t="n"/>
-      <c r="I7" s="15" t="n"/>
-      <c r="J7" s="15" t="n"/>
-      <c r="K7" s="15" t="n"/>
-      <c r="L7" s="15" t="n"/>
-      <c r="M7" s="15" t="n"/>
-      <c r="N7" s="15" t="n"/>
-      <c r="O7" s="15" t="n"/>
-      <c r="P7" s="15" t="n"/>
-      <c r="Q7" s="15" t="n"/>
-      <c r="R7" s="15" t="n"/>
-      <c r="S7" s="15" t="n"/>
-      <c r="T7" s="15" t="n"/>
-      <c r="U7" s="15" t="n"/>
-      <c r="V7" s="15" t="n"/>
-      <c r="W7" s="15" t="n"/>
-      <c r="X7" s="15" t="n"/>
-      <c r="Y7" s="15" t="n"/>
-      <c r="Z7" s="15" t="n"/>
-      <c r="AA7" s="15" t="n"/>
-      <c r="AB7" s="15" t="n"/>
-      <c r="AC7" s="15" t="n"/>
-      <c r="AD7" s="15" t="n"/>
-      <c r="AE7" s="15" t="n"/>
-      <c r="AF7" s="15" t="n"/>
-      <c r="AG7" s="15" t="n"/>
-      <c r="AH7" s="15" t="n"/>
-      <c r="AI7" s="15" t="n"/>
-      <c r="AJ7" s="15" t="n"/>
-      <c r="AK7" s="15" t="n"/>
-      <c r="AL7" s="15" t="n"/>
-      <c r="AM7" s="15" t="n"/>
-      <c r="AN7" s="15" t="n"/>
-      <c r="AO7" s="15" t="n"/>
-      <c r="AP7" s="15" t="n"/>
-      <c r="AQ7" s="15" t="n"/>
-      <c r="AR7" s="15" t="n"/>
-      <c r="AS7" s="15" t="n"/>
-      <c r="AT7" s="15" t="n"/>
-      <c r="AU7" s="15" t="n"/>
-      <c r="AV7" s="15" t="n"/>
-      <c r="AW7" s="13" t="n">
-        <v>0.7755</v>
-      </c>
-      <c r="AX7" s="15" t="n"/>
-      <c r="AY7" s="15" t="n"/>
-      <c r="AZ7" s="15" t="n"/>
-      <c r="BA7" s="15" t="n"/>
-      <c r="BB7" s="15" t="n"/>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="13" t="n"/>
+      <c r="H7" s="13" t="n"/>
+      <c r="I7" s="13" t="n"/>
+      <c r="J7" s="13" t="n"/>
+      <c r="K7" s="13" t="n"/>
+      <c r="L7" s="13" t="n"/>
+      <c r="M7" s="13" t="n"/>
+      <c r="N7" s="13" t="n"/>
+      <c r="O7" s="13" t="n"/>
+      <c r="P7" s="13" t="n"/>
+      <c r="Q7" s="13" t="n"/>
+      <c r="R7" s="13" t="n"/>
+      <c r="S7" s="13" t="n"/>
+      <c r="T7" s="13" t="n"/>
+      <c r="U7" s="13" t="n"/>
+      <c r="V7" s="13" t="n"/>
+      <c r="W7" s="13" t="n"/>
+      <c r="X7" s="13" t="n"/>
+      <c r="Y7" s="13" t="n"/>
+      <c r="Z7" s="13" t="n"/>
+      <c r="AA7" s="13" t="n"/>
+      <c r="AB7" s="13" t="n"/>
+      <c r="AC7" s="13" t="n"/>
+      <c r="AD7" s="13" t="n"/>
+      <c r="AE7" s="13" t="n"/>
+      <c r="AF7" s="13" t="n"/>
+      <c r="AG7" s="13" t="n"/>
+      <c r="AH7" s="13" t="n"/>
+      <c r="AI7" s="13" t="n"/>
+      <c r="AJ7" s="13" t="n"/>
+      <c r="AK7" s="13" t="n"/>
+      <c r="AL7" s="13" t="n"/>
+      <c r="AM7" s="13" t="n"/>
+      <c r="AN7" s="13" t="n"/>
+      <c r="AO7" s="13" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -2794,7 +2480,7 @@
       <c r="X8" s="2" t="n"/>
       <c r="Y8" s="2" t="n"/>
       <c r="Z8" s="9" t="n">
-        <v>0.8905</v>
+        <v>0.8776</v>
       </c>
       <c r="AA8" s="2" t="n"/>
       <c r="AB8" s="2" t="n"/>
@@ -2811,91 +2497,61 @@
       <c r="AM8" s="2" t="n"/>
       <c r="AN8" s="2" t="n"/>
       <c r="AO8" s="2" t="n"/>
-      <c r="AP8" s="2" t="n"/>
-      <c r="AQ8" s="2" t="n"/>
-      <c r="AR8" s="2" t="n"/>
-      <c r="AS8" s="2" t="n"/>
-      <c r="AT8" s="2" t="n"/>
-      <c r="AU8" s="2" t="n"/>
-      <c r="AV8" s="2" t="n"/>
-      <c r="AW8" s="13" t="n">
-        <v>0.8142</v>
-      </c>
-      <c r="AX8" s="2" t="n"/>
-      <c r="AY8" s="2" t="n"/>
-      <c r="AZ8" s="2" t="n"/>
-      <c r="BA8" s="2" t="n"/>
-      <c r="BB8" s="2" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>ext08</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Switchboard operator</t>
         </is>
       </c>
-      <c r="C9" s="15" t="n"/>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="15" t="n"/>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
-      <c r="H9" s="15" t="n"/>
-      <c r="I9" s="15" t="n"/>
-      <c r="J9" s="15" t="n"/>
-      <c r="K9" s="15" t="n"/>
-      <c r="L9" s="15" t="n"/>
-      <c r="M9" s="20" t="n">
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="13" t="n"/>
+      <c r="G9" s="13" t="n"/>
+      <c r="H9" s="13" t="n"/>
+      <c r="I9" s="13" t="n"/>
+      <c r="J9" s="13" t="n"/>
+      <c r="K9" s="13" t="n"/>
+      <c r="L9" s="13" t="n"/>
+      <c r="M9" s="19" t="n">
         <v>0.6401</v>
       </c>
-      <c r="N9" s="15" t="n"/>
-      <c r="O9" s="15" t="n"/>
-      <c r="P9" s="15" t="n"/>
-      <c r="Q9" s="15" t="n"/>
-      <c r="R9" s="15" t="n"/>
-      <c r="S9" s="15" t="n"/>
-      <c r="T9" s="15" t="n"/>
-      <c r="U9" s="15" t="n"/>
-      <c r="V9" s="15" t="n"/>
-      <c r="W9" s="15" t="n"/>
-      <c r="X9" s="15" t="n"/>
-      <c r="Y9" s="15" t="n"/>
+      <c r="N9" s="13" t="n"/>
+      <c r="O9" s="13" t="n"/>
+      <c r="P9" s="13" t="n"/>
+      <c r="Q9" s="13" t="n"/>
+      <c r="R9" s="13" t="n"/>
+      <c r="S9" s="13" t="n"/>
+      <c r="T9" s="13" t="n"/>
+      <c r="U9" s="13" t="n"/>
+      <c r="V9" s="13" t="n"/>
+      <c r="W9" s="13" t="n"/>
+      <c r="X9" s="13" t="n"/>
+      <c r="Y9" s="13" t="n"/>
       <c r="Z9" s="9" t="n">
-        <v>0.8032</v>
-      </c>
-      <c r="AA9" s="15" t="n"/>
-      <c r="AB9" s="15" t="n"/>
-      <c r="AC9" s="15" t="n"/>
-      <c r="AD9" s="15" t="n"/>
-      <c r="AE9" s="15" t="n"/>
-      <c r="AF9" s="15" t="n"/>
-      <c r="AG9" s="15" t="n"/>
-      <c r="AH9" s="15" t="n"/>
-      <c r="AI9" s="15" t="n"/>
-      <c r="AJ9" s="15" t="n"/>
-      <c r="AK9" s="15" t="n"/>
-      <c r="AL9" s="15" t="n"/>
-      <c r="AM9" s="15" t="n"/>
-      <c r="AN9" s="15" t="n"/>
-      <c r="AO9" s="15" t="n"/>
-      <c r="AP9" s="15" t="n"/>
-      <c r="AQ9" s="15" t="n"/>
-      <c r="AR9" s="15" t="n"/>
-      <c r="AS9" s="15" t="n"/>
-      <c r="AT9" s="15" t="n"/>
-      <c r="AU9" s="15" t="n"/>
-      <c r="AV9" s="15" t="n"/>
-      <c r="AW9" s="15" t="n"/>
-      <c r="AX9" s="15" t="n"/>
-      <c r="AY9" s="15" t="n"/>
-      <c r="AZ9" s="13" t="n">
-        <v>0.8276</v>
-      </c>
-      <c r="BA9" s="15" t="n"/>
-      <c r="BB9" s="15" t="n"/>
+        <v>0.8323</v>
+      </c>
+      <c r="AA9" s="13" t="n"/>
+      <c r="AB9" s="13" t="n"/>
+      <c r="AC9" s="13" t="n"/>
+      <c r="AD9" s="13" t="n"/>
+      <c r="AE9" s="13" t="n"/>
+      <c r="AF9" s="13" t="n"/>
+      <c r="AG9" s="13" t="n"/>
+      <c r="AH9" s="13" t="n"/>
+      <c r="AI9" s="13" t="n"/>
+      <c r="AJ9" s="13" t="n"/>
+      <c r="AK9" s="13" t="n"/>
+      <c r="AL9" s="13" t="n"/>
+      <c r="AM9" s="13" t="n"/>
+      <c r="AN9" s="13" t="n"/>
+      <c r="AO9" s="13" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -2922,8 +2578,8 @@
       <c r="N10" s="2" t="n"/>
       <c r="O10" s="2" t="n"/>
       <c r="P10" s="2" t="n"/>
-      <c r="Q10" s="9" t="n">
-        <v>0.7256</v>
+      <c r="Q10" s="18" t="n">
+        <v>0.699</v>
       </c>
       <c r="R10" s="2" t="n"/>
       <c r="S10" s="2" t="n"/>
@@ -2936,7 +2592,7 @@
       <c r="Z10" s="2" t="n"/>
       <c r="AA10" s="2" t="n"/>
       <c r="AB10" s="2" t="n"/>
-      <c r="AC10" s="21" t="n">
+      <c r="AC10" s="20" t="n">
         <v>0.5111</v>
       </c>
       <c r="AD10" s="2" t="n"/>
@@ -2951,21 +2607,6 @@
       <c r="AM10" s="2" t="n"/>
       <c r="AN10" s="2" t="n"/>
       <c r="AO10" s="2" t="n"/>
-      <c r="AP10" s="13" t="n">
-        <v>0.8843</v>
-      </c>
-      <c r="AQ10" s="2" t="n"/>
-      <c r="AR10" s="2" t="n"/>
-      <c r="AS10" s="2" t="n"/>
-      <c r="AT10" s="2" t="n"/>
-      <c r="AU10" s="2" t="n"/>
-      <c r="AV10" s="2" t="n"/>
-      <c r="AW10" s="2" t="n"/>
-      <c r="AX10" s="2" t="n"/>
-      <c r="AY10" s="2" t="n"/>
-      <c r="AZ10" s="2" t="n"/>
-      <c r="BA10" s="2" t="n"/>
-      <c r="BB10" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
